--- a/test123/Main.xlsx
+++ b/test123/Main.xlsx
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="50">
   <si>
     <t>Rule</t>
   </si>
@@ -1045,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:G29"/>
+  <dimension ref="B3:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="2.85546875"/>
@@ -1178,26 +1178,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" t="s" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="s" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="s" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="s" s="1">
-        <v>26</v>
-      </c>
-    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
     <row r="18">
       <c r="B18" s="1" t="s">
         <v>44</v>
@@ -1269,6 +1253,31 @@
       </c>
       <c r="C29" t="s" s="0">
         <v>32</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="s" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="s" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="s" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="1" t="n">
+        <v>234234.0</v>
       </c>
     </row>
   </sheetData>

--- a/test123/Main.xlsx
+++ b/test123/Main.xlsx
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
   <si>
     <t>Rule</t>
   </si>
@@ -343,6 +343,10 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>R10
+qwdqwd</t>
   </si>
 </sst>
 </file>
@@ -393,7 +397,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -424,8 +428,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="41"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill>
+        <fgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill>
+        <fgColor indexed="64"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -646,11 +672,147 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium"/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium"/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium"/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top>
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -682,6 +844,46 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="1" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="2" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="3" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="4" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="1" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="2" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="3" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="4" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="34" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="1" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="34" xfId="0" applyAlignment="true" applyBorder="true" applyNumberFormat="true" applyFill="true" applyFont="true" quotePrefix="false">
+      <alignment horizontal="general" vertical="bottom" indent="2" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection hidden="false" locked="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1077,7 +1279,7 @@
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="31" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -1123,8 +1325,8 @@
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="15" t="s">
-        <v>9</v>
+      <c r="B8" s="37" t="s">
+        <v>50</v>
       </c>
       <c r="C8" s="16">
         <v>0</v>
